--- a/SS_floodwall_input.xlsx
+++ b/SS_floodwall_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\Task_FY25_NCMP_Part_1\Exceedance_code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5182B439-F5A2-454A-88E9-CF4FD6AB4B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4226C9-3649-47D9-83E9-0BA3CA327E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
   </bookViews>
   <sheets>
     <sheet name="FloodWall" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
   <si>
     <t>NA</t>
   </si>
@@ -531,6 +531,15 @@
   </si>
   <si>
     <t>StormSim Project General Inputs</t>
+  </si>
+  <si>
+    <t>calc_wave_transmission</t>
+  </si>
+  <si>
+    <t>compute_wave_transmission</t>
+  </si>
+  <si>
+    <t>Compute wave transmission (eurotop)</t>
   </si>
 </sst>
 </file>
@@ -540,7 +549,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,6 +591,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="13">
@@ -844,7 +859,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -985,6 +1000,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1301,7 +1319,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDE711C-012D-4C9C-BCEB-7FA13A47BF68}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.7109375" customWidth="1"/>
@@ -2332,10 +2350,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>13</v>
+        <v>167</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>0</v>
@@ -2346,66 +2364,66 @@
     </row>
     <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D55" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="10">
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>0</v>
@@ -2414,27 +2432,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B60" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="C60" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-    </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="60" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>

--- a/SS_floodwall_input.xlsx
+++ b/SS_floodwall_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_StormSim_Task\StormSim-Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4226C9-3649-47D9-83E9-0BA3CA327E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD982B7-8048-4CB7-B202-370B02859C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="23955" windowHeight="20985" xr2:uid="{392BD468-0951-485E-9EDB-F7D879C79477}"/>
   </bookViews>
   <sheets>
     <sheet name="FloodWall" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="132">
   <si>
     <t>NA</t>
   </si>
@@ -119,42 +119,12 @@
     <t>water_density</t>
   </si>
   <si>
-    <t>Armor Immersed Relative Density Delta</t>
-  </si>
-  <si>
-    <t>armor_delta</t>
-  </si>
-  <si>
     <t>Structure Properties</t>
   </si>
   <si>
     <t>[m]</t>
   </si>
   <si>
-    <t>Berm Elevation (Negative Below Datum Zero)</t>
-  </si>
-  <si>
-    <t>berm_elevation</t>
-  </si>
-  <si>
-    <t>Berm Width</t>
-  </si>
-  <si>
-    <t>berm_width</t>
-  </si>
-  <si>
-    <t>Wall Seaward Slope (Same Slope Is Assumed For Landward Slope)</t>
-  </si>
-  <si>
-    <t>berm_slope</t>
-  </si>
-  <si>
-    <t>Add berm in front of structure seaward side (0- No Berm/ 1- Add Berm)</t>
-  </si>
-  <si>
-    <t>add_berm</t>
-  </si>
-  <si>
     <t>Bottom of Wall Elevation (Applies to wall type structures)</t>
   </si>
   <si>
@@ -236,33 +206,9 @@
     <t>pros_compute_forcing_HC</t>
   </si>
   <si>
-    <t>Probability Masses (CHS -&gt; Probability_Masses folder relative path, Custom Modeling -&gt; .mat filename with relative path)</t>
-  </si>
-  <si>
-    <t>prob_mass_source</t>
-  </si>
-  <si>
-    <t>Chicago_files</t>
-  </si>
-  <si>
-    <t>CHS Region Grid File (Relative Path)</t>
-  </si>
-  <si>
-    <t>chs_grid_file_source</t>
-  </si>
-  <si>
     <t>StormSim: Probabilistic Run-up, Overtopping &amp; Stone Sizing (PROS)</t>
   </si>
   <si>
-    <t>Chicago_files\CHS-GLMH_ADCIRC_BiasUncertainty_perVG_rta.mat</t>
-  </si>
-  <si>
-    <t>CHS Region Bias File (Relative Path)</t>
-  </si>
-  <si>
-    <t>chs_ssl_bias_and_uncertainty_file</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
@@ -383,42 +329,18 @@
     <t>apply_depth_limitation</t>
   </si>
   <si>
-    <t>Runup Uncertainty</t>
-  </si>
-  <si>
-    <t>r2p_u</t>
-  </si>
-  <si>
     <t>Apply random tide to storm SWL (0 - Off / 1 - On)</t>
   </si>
   <si>
     <t>apply_random_tides</t>
   </si>
   <si>
-    <t>[m^3/s/m]</t>
-  </si>
-  <si>
-    <t>Overtopping Uncertainty</t>
-  </si>
-  <si>
-    <t>q_u</t>
-  </si>
-  <si>
     <t>Sea level rise applied as vertical offset to SWL.</t>
   </si>
   <si>
     <t>swl_slr</t>
   </si>
   <si>
-    <t>[N/m^2]</t>
-  </si>
-  <si>
-    <t>Surface Pressure (p1) Uncertainty' (Floodwalls Only)</t>
-  </si>
-  <si>
-    <t>p1_u</t>
-  </si>
-  <si>
     <t>XC</t>
   </si>
   <si>
@@ -428,12 +350,6 @@
     <t>storm_sampling</t>
   </si>
   <si>
-    <t>Dn50 Uncertainty</t>
-  </si>
-  <si>
-    <t>dn50_u</t>
-  </si>
-  <si>
     <t>Structure type  (Levee - 1, Floodwalls - 2, Rubblemound - 3)</t>
   </si>
   <si>
@@ -446,9 +362,6 @@
     <t>workflow</t>
   </si>
   <si>
-    <t>StormSim Project Structure Response Uncertainty</t>
-  </si>
-  <si>
     <t>[84 90]</t>
   </si>
   <si>
@@ -467,12 +380,6 @@
     <t>project_datum</t>
   </si>
   <si>
-    <t>Hm0 Proportional Uncertainty, U_r</t>
-  </si>
-  <si>
-    <t>chs_hm0_u_r</t>
-  </si>
-  <si>
     <t>SS_Outputs_7175_T3</t>
   </si>
   <si>
@@ -482,12 +389,6 @@
     <t>outfolder</t>
   </si>
   <si>
-    <t>Hm0 Absolute Uncertainty, U_a</t>
-  </si>
-  <si>
-    <t>chs_hm0_u_a</t>
-  </si>
-  <si>
     <t>Seawall_existing</t>
   </si>
   <si>
@@ -497,12 +398,6 @@
     <t>case_name</t>
   </si>
   <si>
-    <t>SWL Proportional Uncertainty, U_r</t>
-  </si>
-  <si>
-    <t>chs_swl_u_r</t>
-  </si>
-  <si>
     <t>R7175_T3</t>
   </si>
   <si>
@@ -512,12 +407,6 @@
     <t>struc_id</t>
   </si>
   <si>
-    <t>SWL Absolute Uncertainty, U_a</t>
-  </si>
-  <si>
-    <t>chs_swl_u_a</t>
-  </si>
-  <si>
     <t>Chicago Shoreline GRR</t>
   </si>
   <si>
@@ -527,29 +416,29 @@
     <t>project_name</t>
   </si>
   <si>
-    <t xml:space="preserve">StormSim Project Forcing Uncertainty </t>
-  </si>
-  <si>
     <t>StormSim Project General Inputs</t>
   </si>
   <si>
-    <t>calc_wave_transmission</t>
-  </si>
-  <si>
     <t>compute_wave_transmission</t>
   </si>
   <si>
     <t>Compute wave transmission (eurotop)</t>
+  </si>
+  <si>
+    <t>chs_dependencies</t>
+  </si>
+  <si>
+    <t>CHS regional dependencies folder</t>
+  </si>
+  <si>
+    <t>..\CHS_Dependencies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,14 +468,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -599,7 +480,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,14 +547,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -809,8 +684,10 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -820,32 +697,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -855,11 +706,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -928,14 +778,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -960,12 +802,8 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -975,37 +813,24 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1319,7 +1144,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDE711C-012D-4C9C-BCEB-7FA13A47BF68}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.7109375" customWidth="1"/>
@@ -1333,25 +1158,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="F1" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="A1" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="F1" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>18</v>
@@ -1374,152 +1203,152 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="G3" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="57">
-        <v>9.3515882748499979E-2</v>
+        <v>123</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="44">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="56" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" s="57">
-        <v>0.35632805802324996</v>
+        <v>120</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="10">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="G5" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="31">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="31">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>0</v>
@@ -1527,25 +1356,25 @@
       <c r="D9" s="10">
         <v>1</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>17</v>
+      <c r="F9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>0</v>
@@ -1553,77 +1382,69 @@
       <c r="D10" s="6">
         <v>2</v>
       </c>
-      <c r="F10" s="54" t="s">
-        <v>131</v>
+      <c r="F10" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" s="10">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0.43</v>
+        <v>101</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="30">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" s="10">
         <v>176.45</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0.78</v>
-      </c>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>0</v>
@@ -1631,25 +1452,19 @@
       <c r="D13" s="10">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="33">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F13" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>0</v>
@@ -1657,17 +1472,25 @@
       <c r="D14" s="10">
         <v>1</v>
       </c>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>0</v>
@@ -1675,23 +1498,25 @@
       <c r="D15" s="10">
         <v>0</v>
       </c>
-      <c r="F15" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="I15" s="47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>0</v>
@@ -1699,25 +1524,25 @@
       <c r="D16" s="10">
         <v>1</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>17</v>
+      <c r="F16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>0</v>
@@ -1725,25 +1550,25 @@
       <c r="D17" s="10">
         <v>0</v>
       </c>
-      <c r="F17" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="48">
-        <v>1000</v>
+      <c r="F17" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>0</v>
@@ -1752,24 +1577,24 @@
         <v>0</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="I18" s="10">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>0</v>
@@ -1777,17 +1602,25 @@
       <c r="D19" s="10">
         <v>1</v>
       </c>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
+      <c r="F19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>0</v>
@@ -1795,83 +1628,53 @@
       <c r="D20" s="10">
         <v>1</v>
       </c>
-      <c r="F20" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>17</v>
+      <c r="D21" s="30" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="45"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="F22" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="21">
-        <v>0</v>
-      </c>
+      <c r="A22" s="41"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="F23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I23" s="10">
-        <v>0</v>
-      </c>
+      <c r="A23" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>18</v>
@@ -1879,603 +1682,387 @@
       <c r="D24" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>80</v>
+        <v>63</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>62</v>
       </c>
       <c r="D25" s="21">
         <v>1</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="33">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>57</v>
       </c>
       <c r="D26" s="21">
         <v>2.46</v>
       </c>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="B32" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="C32" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="D32" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I29" s="21">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="27">
+        <v>180.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="6">
+        <v>175.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="17">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I31" s="10">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="F32" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="F33" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="I34" s="33">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="30">
-        <v>180.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="6">
-        <v>175.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-    </row>
-    <row r="44" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-    </row>
-    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="21">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="17">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-    </row>
-    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>17</v>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="10">
+        <v>4</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="10">
+    <row r="53" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="C53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="60" t="s">
-        <v>165</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="50"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>
-    <protectedRange sqref="I3:I6 I10:I14 I22:I25 I29 I17:I18" name="Range1_1"/>
-    <protectedRange sqref="D46:D48" name="Range1_1_4"/>
+    <protectedRange sqref="I15 I3:I4 I8:I11" name="Range1_1"/>
+    <protectedRange sqref="D40:D41" name="Range1_1_4"/>
     <protectedRange sqref="D14 D16:D18 D9:D12 D6" name="Range1_1_1"/>
     <protectedRange sqref="D8 D15" name="Range1_1_1_1"/>
     <protectedRange sqref="D13" name="Range1_1_2"/>
@@ -2483,18 +2070,14 @@
     <protectedRange sqref="D4" name="Range1_1_8"/>
     <protectedRange sqref="D5" name="Range1_1_7"/>
     <protectedRange sqref="D7" name="Range1_1_5"/>
-    <protectedRange sqref="D25" name="Range1_1_3_3"/>
-    <protectedRange sqref="D31" name="Range1_1_2_1_1"/>
-    <protectedRange sqref="D28" name="Range1_1_5_1_1_1_1"/>
-    <protectedRange sqref="D26" name="Range1_1_5_2"/>
-    <protectedRange sqref="D27" name="Range1_1_6_1"/>
-    <protectedRange sqref="D29" name="Range1_1_5_1_1"/>
-    <protectedRange sqref="D30" name="Range1_1_8_1_1"/>
-    <protectedRange sqref="D35" name="Range1_1_3_1_3"/>
-    <protectedRange sqref="D40 D38" name="Range1_1_3_1_1"/>
-    <protectedRange sqref="D39" name="Range1_1_3_1_2_1"/>
-    <protectedRange sqref="D36" name="Range1_1_3_1_4"/>
-    <protectedRange sqref="D37" name="Range1_1_3_1_5"/>
+    <protectedRange sqref="D33" name="Range1_1_3_1_3"/>
+    <protectedRange sqref="D36" name="Range1_1_3_1_1"/>
+    <protectedRange sqref="D34" name="Range1_1_3_1_4"/>
+    <protectedRange sqref="D35" name="Range1_1_3_1_5"/>
+    <protectedRange sqref="D25" name="Range1_1_3_3_2"/>
+    <protectedRange sqref="D29" name="Range1_1_2_1_1_2"/>
+    <protectedRange sqref="D26:D27" name="Range1_1_5_2_2"/>
+    <protectedRange sqref="D28" name="Range1_1_8_1_1_2"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
